--- a/BWI/bestwine_output/bestwine_Ecuador.xlsx
+++ b/BWI/bestwine_output/bestwine_Ecuador.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA77"/>
+  <dimension ref="A1:AA79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8752,6 +8752,208 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador Premium Brands Epb S.a.</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador Premium Brands Epb S.a.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>110643</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Pichincha, Distrito Metropolitano de Quito</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Calle G N51-29 Y Av. De Los Álamos Guayaquil: Ciudadela Vernaza Norte Mz 13 Villa #4a</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>170149</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://epbvinosylicores.com, https://tienda.epbvinosylicores.com</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>info@epb.ec</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>1792911036001</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EPBVinosyLicores</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCFv8Fp10DpqoMI4YVz68khA</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Castellanos</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jorge-castellanos-510a471b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador Premium Brands Epb S.a.</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador Premium Brands Epb S.a.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>110643</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Pichincha, Distrito Metropolitano de Quito</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Calle G N51-29 Y Av. De Los Álamos Guayaquil: Ciudadela Vernaza Norte Mz 13 Villa #4a</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>170149</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://epbvinosylicores.com, https://tienda.epbvinosylicores.com</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>info@epb.ec</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>1792911036001</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EPBVinosyLicores</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCFv8Fp10DpqoMI4YVz68khA</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>Fernando Vivanco</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vivancofernando/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ecuador.xlsx
+++ b/BWI/bestwine_output/bestwine_Ecuador.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA79"/>
+  <dimension ref="A1:AA81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8954,6 +8954,208 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador Premium Brands Epb S.a.</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador Premium Brands Epb S.a.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>110643</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Pichincha, Distrito Metropolitano de Quito</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Calle G N51-29 Y Av. De Los Álamos Guayaquil: Ciudadela Vernaza Norte Mz 13 Villa #4a</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>170149</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://epbvinosylicores.com, https://tienda.epbvinosylicores.com</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>info@epb.ec</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>1792911036001</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EPBVinosyLicores</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCFv8Fp10DpqoMI4YVz68khA</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Castellanos</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jorge-castellanos-510a471b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador Premium Brands Epb S.a.</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador Premium Brands Epb S.a.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>110643</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Pichincha, Distrito Metropolitano de Quito</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Calle G N51-29 Y Av. De Los Álamos Guayaquil: Ciudadela Vernaza Norte Mz 13 Villa #4a</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>170149</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://epbvinosylicores.com, https://tienda.epbvinosylicores.com</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>info@epb.ec</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>1792911036001</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EPBVinosyLicores</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCFv8Fp10DpqoMI4YVz68khA</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>Fernando Vivanco</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vivancofernando/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
